--- a/data/ams_weekly_data/White_Mulberry/business_report_week27.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/business_report_week27.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W9"/>
+  <dimension ref="A1:W26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -536,27 +536,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FBA79476</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>WM-GS1M-BK</t>
+          <t>WM-LOD-WH</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
+          <t>B0BFVMDJ2K</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>WM-LOD-WH</t>
+        </is>
+      </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>2471</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -568,7 +572,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>3431</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -586,7 +590,7 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -598,7 +602,7 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>84764.27</v>
+        <v>60208.91</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -613,27 +617,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FBA79477</t>
+          <t>FBA76418</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>WM-GS2M-BK</t>
+          <t>WM-LOD-IN</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0BFVNS8HS</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
+          <t>B0BFVNS8HS</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>WM-LOD-IN</t>
+        </is>
+      </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>603</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -645,7 +653,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>747</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -675,7 +683,7 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>14051.71</v>
+        <v>27903.39</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -690,27 +698,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FBA79478</t>
+          <t>FBA76416</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>WM-HA1M-BK</t>
+          <t>WM-LOD-BK</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+          <t>B0BFW59TRG</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>WM-LOD-BK</t>
+        </is>
+      </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>237</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -722,7 +734,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>324</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -740,7 +752,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -752,7 +764,7 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>6871.19</v>
+        <v>20031.36</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -767,27 +779,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FBA79479</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>WM-HA2M-BK</t>
+          <t>WM-LOD-CF</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+          <t>B0BFWD6SNF</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>WM-LOD-CF</t>
+        </is>
+      </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1548</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -799,7 +815,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2331</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -817,7 +833,7 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -829,7 +845,7 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>28657.68</v>
+        <v>76236.44</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -844,27 +860,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FBA79613</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MS1ML</t>
+          <t>WM-GD07-CB</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B0DP2VVRND</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>B0DP2VVRND</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
+          <t>B0CPFS24ML</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>WM-GD07-CB</t>
+        </is>
+      </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>6474</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -876,7 +896,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>9650</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -894,7 +914,7 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -906,7 +926,7 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>53362.62</v>
+        <v>359102.54</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -921,27 +941,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FBA79612</t>
+          <t>FBA79179</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>WM1ML</t>
+          <t>WM-SE08-CF</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
+          <t>B0CPT3Q25C</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>WM-SE08-CF</t>
+        </is>
+      </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1029</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -953,7 +977,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1371</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -971,7 +995,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -983,7 +1007,7 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>24576.27</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -998,27 +1022,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FBA79616</t>
+          <t>FBA79476</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HD1ML</t>
+          <t>WM-GS1M-BK</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B0DP3194QN</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>B0DP3194QN</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>WM-GS1M-BK</t>
+        </is>
+      </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>2468</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -1030,7 +1058,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>3511</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1048,7 +1076,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1060,7 +1088,7 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>84764.27</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -1075,27 +1103,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FBA79617</t>
+          <t>FBA79477</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HDWF1ML</t>
+          <t>WM-GS2M-BK</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
+          <t>B0DB5VVPSB</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>WM-GS2M-BK</t>
+        </is>
+      </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>806</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -1107,7 +1139,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1149</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1137,15 +1169,1392 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
+        <v>32959.34</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FBA79478</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>WM-HA1M-BK</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>B0DB5W4TCP</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>B0DB5W4TCP</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>WM-HA1M-BK</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>760</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1112</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>6871.19</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>FBA79479</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>WM-HA2M-BK</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>B0DB5YTQZV</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>B0DB5YTQZV</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>WM-HA2M-BK</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1048</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1418</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>28657.68</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>FBA79613</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>MS1ML</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>B0DP2VVRND</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>B0DP2VVRND</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>MS1ML</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>2742</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>4028</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>46</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>77164.32000000001</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>FBA79612</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>WM1ML</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>B0DP2WC5VW</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>B0DP2WC5VW</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>WM1ML</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>642</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>859</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>55939.83</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>FBA79615</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>VLMS1ML</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>B0DP2Z5DQ9</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>B0DP2Z5DQ9</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>VLMS1ML</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>449</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>575</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>9488.139999999999</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>FBA79614</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>MS2ML</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>B0DP313R77</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>B0DP313R77</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>MS2ML</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>141</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>185</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>6702.54</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>FBA79616</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>HD1ML</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>B0DP3194QN</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>B0DP3194QN</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>HD1ML</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>130</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>195</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>FBA79617</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>HDWF1ML</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>B0DP32F346</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>B0DP32F346</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>HDWF1ML</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1007</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1357</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
         <v>23369.49</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>FBA79662</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>WM-MODL-WH</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>B0DQ4YWSMC</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>B0DQ4YWSMC</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>WM-MODL-WH</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>894</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1162</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>25298.3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>FBA79790</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>TVLF1ML</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>B0FHVWHQHR</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>B0FHVWHQHR</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>TVLF1ML</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>130</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>202</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>7474.58</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>FBK79788</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>TVCT1ML</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>B0FN4D3C89</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>B0FN4D3C89</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>TVCT1ML</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>68</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>105</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1454.24</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>FBK79789</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>TVMF1ML</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>B0FN4DSQ6P</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>B0FN4DSQ6P</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>TVMF1ML</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>847</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1470</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>103</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>50014.41</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>FBK79784</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>POS2M</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>B0FN4FHH5Y</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>B0FN4FHH5Y</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>POS2M</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>17</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>21</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>4660.17</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>FBK79786</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>POSS-01</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>B0FN4FPJ83</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>B0FN4FPJ83</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>POSS-01</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>48</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>69</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>8385.59</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>FBK79787</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>TVCF1ML</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>B0FN4GQ9HT</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>B0FN4GQ9HT</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>TVCF1ML</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>231</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>321</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>6162.71</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>FBK79791</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>TVFM1ML</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>B0FN4HDM6Z</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>B0FN4HDM6Z</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>TVFM1ML</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>257</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>302</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3557.63</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>FBK79792</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>HDMSP1ML</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>B0FN4JG97R</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>B0FN4JG97R</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>HDMSP1ML</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>165</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>204</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>28740.68</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/ams_weekly_data/White_Mulberry/business_report_week27.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/business_report_week27.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,117 +429,117 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>SKU</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>(Parent) ASIN</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>(Child) ASIN</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Sessions - Total</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Sessions - Total - B2B</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Session Percentage - Total</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Session Percentage - Total - B2B</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Page Views - Total</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Page Views - Total - B2B</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Page Views Percentage - Total</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Page Views Percentage - Total - B2B</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Featured Offer Percentage</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Featured Offer Percentage - B2B</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>units_ordered</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Units Ordered - B2B</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Unit Session Percentage</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Unit Session Percentage - B2B</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>ordered_product_sales</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Ordered Product Sales - B2B</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Total Order Items</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Total Order Items - B2B</t>
         </is>
@@ -1076,7 +1088,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1088,7 +1100,7 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>84764.27</v>
+        <v>127967.57</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -1157,7 +1169,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1169,7 +1181,7 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>32959.34</v>
+        <v>36428.84</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -1238,7 +1250,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -1250,7 +1262,7 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>6871.19</v>
+        <v>8183.9</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -1319,7 +1331,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1331,7 +1343,7 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>28657.68</v>
+        <v>43141.97</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -1400,7 +1412,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -1412,7 +1424,7 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>77164.32000000001</v>
+        <v>83651.60000000001</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -1724,7 +1736,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -1736,7 +1748,7 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>8895.77</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -1805,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -1817,7 +1829,7 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>23369.49</v>
+        <v>38593.2</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
